--- a/totales_x_distrito_por_fecha.xlsx
+++ b/totales_x_distrito_por_fecha.xlsx
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
         <v>2</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
         <v>2</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
         <v>2</v>
@@ -4691,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
         <v>2</v>
@@ -30961,7 +30961,7 @@
         <v>0</v>
       </c>
       <c r="H825" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I825" t="n">
         <v>4</v>
@@ -30998,7 +30998,7 @@
         <v>0</v>
       </c>
       <c r="H826" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I826" t="n">
         <v>4</v>
@@ -42616,7 +42616,7 @@
         <v>0</v>
       </c>
       <c r="H1140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1140" t="n">
         <v>2</v>

--- a/totales_x_distrito_por_fecha.xlsx
+++ b/totales_x_distrito_por_fecha.xlsx
@@ -30998,7 +30998,7 @@
         <v>0</v>
       </c>
       <c r="H826" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I826" t="n">
         <v>4</v>

--- a/totales_x_distrito_por_fecha.xlsx
+++ b/totales_x_distrito_por_fecha.xlsx
@@ -3214,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -8237,7 +8237,7 @@
         <v>46136</v>
       </c>
       <c r="F211" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -14721,7 +14721,7 @@
         <v>0</v>
       </c>
       <c r="I386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -14795,7 +14795,7 @@
         <v>0</v>
       </c>
       <c r="I388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="I663" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="664">
@@ -25072,7 +25072,7 @@
         <v>46135</v>
       </c>
       <c r="F666" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G666" t="n">
         <v>0</v>
@@ -25858,7 +25858,7 @@
         <v>0</v>
       </c>
       <c r="I687" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="688">
@@ -28078,7 +28078,7 @@
         <v>0</v>
       </c>
       <c r="I747" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="748">
@@ -28115,7 +28115,7 @@
         <v>0</v>
       </c>
       <c r="I748" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="749">
@@ -31260,7 +31260,7 @@
         <v>0</v>
       </c>
       <c r="I833" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="834">
@@ -33628,7 +33628,7 @@
         <v>0</v>
       </c>
       <c r="I897" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="898">
@@ -33656,7 +33656,7 @@
         <v>46136</v>
       </c>
       <c r="F898" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G898" t="n">
         <v>0</v>
@@ -34109,7 +34109,7 @@
         <v>0</v>
       </c>
       <c r="I910" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="911">
@@ -34775,7 +34775,7 @@
         <v>0</v>
       </c>
       <c r="I928" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="929">
@@ -35959,7 +35959,7 @@
         <v>0</v>
       </c>
       <c r="I960" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="961">
@@ -37624,7 +37624,7 @@
         <v>0</v>
       </c>
       <c r="I1005" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1006">
@@ -38253,7 +38253,7 @@
         <v>0</v>
       </c>
       <c r="I1022" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1023">
@@ -40436,7 +40436,7 @@
         <v>0</v>
       </c>
       <c r="I1081" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1082">
@@ -40658,7 +40658,7 @@
         <v>0</v>
       </c>
       <c r="I1087" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1088">
@@ -41916,7 +41916,7 @@
         <v>0</v>
       </c>
       <c r="I1121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1122">
@@ -43424,7 +43424,7 @@
         <v>46136</v>
       </c>
       <c r="F1162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1162" t="n">
         <v>0</v>
@@ -43720,7 +43720,7 @@
         <v>46135</v>
       </c>
       <c r="F1170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1170" t="n">
         <v>0</v>

--- a/totales_x_distrito_por_fecha.xlsx
+++ b/totales_x_distrito_por_fecha.xlsx
@@ -1984,7 +1984,7 @@
         <v>46135</v>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -4130,7 +4130,7 @@
         <v>46136</v>
       </c>
       <c r="F100" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
         <v>46136</v>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -12788,7 +12788,7 @@
         <v>46136</v>
       </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G334" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
         <v>46134</v>
       </c>
       <c r="F389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G389" t="n">
         <v>0</v>
@@ -19337,7 +19337,7 @@
         <v>46136</v>
       </c>
       <c r="F511" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G511" t="n">
         <v>0</v>
@@ -33212,7 +33212,7 @@
         <v>46136</v>
       </c>
       <c r="F886" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G886" t="n">
         <v>0</v>
@@ -44682,7 +44682,7 @@
         <v>46134</v>
       </c>
       <c r="F1196" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1196" t="n">
         <v>0</v>
@@ -45200,7 +45200,7 @@
         <v>46136</v>
       </c>
       <c r="F1210" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G1210" t="n">
         <v>0</v>

--- a/totales_x_distrito_por_fecha.xlsx
+++ b/totales_x_distrito_por_fecha.xlsx
@@ -54428,7 +54428,7 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>140611</t>
+          <t>140608</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
@@ -54443,7 +54443,7 @@
       </c>
       <c r="D1460" t="inlineStr">
         <is>
-          <t>LANGA</t>
+          <t>HUANZA</t>
         </is>
       </c>
       <c r="E1460" s="2" t="n">
@@ -54453,7 +54453,7 @@
         <v>0</v>
       </c>
       <c r="G1460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1460" t="n">
         <v>0</v>
@@ -54465,7 +54465,7 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>140611</t>
+          <t>140608</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
@@ -54480,7 +54480,7 @@
       </c>
       <c r="D1461" t="inlineStr">
         <is>
-          <t>LANGA</t>
+          <t>HUANZA</t>
         </is>
       </c>
       <c r="E1461" s="2" t="n">
@@ -54496,13 +54496,13 @@
         <v>0</v>
       </c>
       <c r="I1461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>140611</t>
+          <t>140608</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
@@ -54517,7 +54517,7 @@
       </c>
       <c r="D1462" t="inlineStr">
         <is>
-          <t>LANGA</t>
+          <t>HUANZA</t>
         </is>
       </c>
       <c r="E1462" s="2" t="n">
@@ -54539,7 +54539,7 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>140611</t>
+          <t>140608</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
@@ -54554,7 +54554,7 @@
       </c>
       <c r="D1463" t="inlineStr">
         <is>
-          <t>LANGA</t>
+          <t>HUANZA</t>
         </is>
       </c>
       <c r="E1463" s="2" t="n">
@@ -54570,13 +54570,13 @@
         <v>0</v>
       </c>
       <c r="I1463" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>140611</t>
+          <t>140608</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
@@ -54591,7 +54591,7 @@
       </c>
       <c r="D1464" t="inlineStr">
         <is>
-          <t>LANGA</t>
+          <t>HUANZA</t>
         </is>
       </c>
       <c r="E1464" s="2" t="n">
@@ -54604,7 +54604,7 @@
         <v>0</v>
       </c>
       <c r="H1464" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1464" t="n">
         <v>2</v>
@@ -54613,7 +54613,7 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>140611</t>
+          <t>140608</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
@@ -54628,7 +54628,7 @@
       </c>
       <c r="D1465" t="inlineStr">
         <is>
-          <t>LANGA</t>
+          <t>HUANZA</t>
         </is>
       </c>
       <c r="E1465" s="2" t="n">
@@ -54650,7 +54650,7 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>140611</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
@@ -54665,7 +54665,7 @@
       </c>
       <c r="D1466" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>LANGA</t>
         </is>
       </c>
       <c r="E1466" s="2" t="n">
@@ -54681,13 +54681,13 @@
         <v>0</v>
       </c>
       <c r="I1466" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>140611</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
@@ -54702,7 +54702,7 @@
       </c>
       <c r="D1467" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>LANGA</t>
         </is>
       </c>
       <c r="E1467" s="2" t="n">
@@ -54718,13 +54718,13 @@
         <v>0</v>
       </c>
       <c r="I1467" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>140611</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
@@ -54739,7 +54739,7 @@
       </c>
       <c r="D1468" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>LANGA</t>
         </is>
       </c>
       <c r="E1468" s="2" t="n">
@@ -54755,13 +54755,13 @@
         <v>0</v>
       </c>
       <c r="I1468" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>140611</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
@@ -54776,7 +54776,7 @@
       </c>
       <c r="D1469" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>LANGA</t>
         </is>
       </c>
       <c r="E1469" s="2" t="n">
@@ -54792,13 +54792,13 @@
         <v>0</v>
       </c>
       <c r="I1469" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>140611</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
@@ -54813,29 +54813,29 @@
       </c>
       <c r="D1470" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>LANGA</t>
         </is>
       </c>
       <c r="E1470" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="F1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1470" t="n">
         <v>1</v>
       </c>
-      <c r="G1470" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1470" t="n">
-        <v>0</v>
-      </c>
       <c r="I1470" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>140611</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
@@ -54850,7 +54850,7 @@
       </c>
       <c r="D1471" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>LANGA</t>
         </is>
       </c>
       <c r="E1471" s="2" t="n">
@@ -54872,7 +54872,7 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>140608</t>
+          <t>140631</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
@@ -54887,7 +54887,7 @@
       </c>
       <c r="D1472" t="inlineStr">
         <is>
-          <t>LUNES 27</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="E1472" s="2" t="n">
@@ -54903,13 +54903,13 @@
         <v>0</v>
       </c>
       <c r="I1472" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>140608</t>
+          <t>140631</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
@@ -54924,7 +54924,7 @@
       </c>
       <c r="D1473" t="inlineStr">
         <is>
-          <t>LUNES 27</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="E1473" s="2" t="n">
@@ -54940,13 +54940,13 @@
         <v>0</v>
       </c>
       <c r="I1473" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>140608</t>
+          <t>140631</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
@@ -54961,7 +54961,7 @@
       </c>
       <c r="D1474" t="inlineStr">
         <is>
-          <t>LUNES 27</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="E1474" s="2" t="n">
@@ -54977,13 +54977,13 @@
         <v>0</v>
       </c>
       <c r="I1474" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>140608</t>
+          <t>140631</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
@@ -54998,7 +54998,7 @@
       </c>
       <c r="D1475" t="inlineStr">
         <is>
-          <t>LUNES 27</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="E1475" s="2" t="n">
@@ -55014,13 +55014,13 @@
         <v>0</v>
       </c>
       <c r="I1475" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>140608</t>
+          <t>140631</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
@@ -55035,14 +55035,14 @@
       </c>
       <c r="D1476" t="inlineStr">
         <is>
-          <t>LUNES 27</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="E1476" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="F1476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -55051,13 +55051,13 @@
         <v>0</v>
       </c>
       <c r="I1476" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>140608</t>
+          <t>140631</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
@@ -55072,7 +55072,7 @@
       </c>
       <c r="D1477" t="inlineStr">
         <is>
-          <t>LUNES 27</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="E1477" s="2" t="n">
@@ -63117,7 +63117,7 @@
         <v>0</v>
       </c>
       <c r="I1694" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1695">
@@ -63154,7 +63154,7 @@
         <v>0</v>
       </c>
       <c r="I1695" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1696">
@@ -63191,7 +63191,7 @@
         <v>0</v>
       </c>
       <c r="I1696" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1697">
@@ -63228,7 +63228,7 @@
         <v>0</v>
       </c>
       <c r="I1697" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1698">
@@ -63265,7 +63265,7 @@
         <v>0</v>
       </c>
       <c r="I1698" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1699">
@@ -68408,7 +68408,7 @@
         <v>0</v>
       </c>
       <c r="I1837" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1838">

--- a/totales_x_distrito_por_fecha.xlsx
+++ b/totales_x_distrito_por_fecha.xlsx
@@ -15896,7 +15896,7 @@
         <v>46136</v>
       </c>
       <c r="F418" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
@@ -15933,7 +15933,7 @@
         <v>46137</v>
       </c>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G419" t="n">
         <v>0</v>
